--- a/demo 2 (alpha)/Pb210_results/CFCS modeling data/MAR_model_summaries.xlsx
+++ b/demo 2 (alpha)/Pb210_results/CFCS modeling data/MAR_model_summaries.xlsx
@@ -403,19 +403,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>2.551448088165256</v>
+        <v>2.551008093705098</v>
       </c>
       <c r="D2">
-        <v>0.04763678128609765</v>
+        <v>0.04773585148413886</v>
       </c>
       <c r="E2">
-        <v>53.56046355948638</v>
+        <v>53.44008778292598</v>
       </c>
       <c r="F2">
-        <v>3.853533179501429E-28</v>
+        <v>4.083615388291089E-28</v>
       </c>
       <c r="G2">
-        <v>0.9492261474982776</v>
+        <v>0.9492972744115757</v>
       </c>
     </row>
     <row r="3">
@@ -430,19 +430,19 @@
         </is>
       </c>
       <c r="C3">
-        <v>-0.2370597732356239</v>
+        <v>-0.2377279094982346</v>
       </c>
       <c r="D3">
-        <v>0.01054099068538749</v>
+        <v>0.01056291278017555</v>
       </c>
       <c r="E3">
-        <v>-22.48932574850382</v>
+        <v>-22.50590480538681</v>
       </c>
       <c r="F3">
-        <v>1.447491431408781E-18</v>
+        <v>1.421304023385128E-18</v>
       </c>
       <c r="G3">
-        <v>0.9492261474982776</v>
+        <v>0.9492972744115757</v>
       </c>
     </row>
     <row r="4">
@@ -457,19 +457,19 @@
         </is>
       </c>
       <c r="C4">
-        <v>5.681448677902043</v>
+        <v>5.742922328111714</v>
       </c>
       <c r="D4">
-        <v>0.3635039574996146</v>
+        <v>0.3688792422295571</v>
       </c>
       <c r="E4">
-        <v>15.62967489262635</v>
+        <v>15.56857006482853</v>
       </c>
       <c r="F4">
-        <v>4.344437819635491E-06</v>
+        <v>4.445553485700412E-06</v>
       </c>
       <c r="G4">
-        <v>0.9714823929119137</v>
+        <v>0.9714077248880298</v>
       </c>
     </row>
     <row r="5">
@@ -484,19 +484,19 @@
         </is>
       </c>
       <c r="C5">
-        <v>-0.6261707906785706</v>
+        <v>-0.6345791751314126</v>
       </c>
       <c r="D5">
-        <v>0.04046449720400426</v>
+        <v>0.04106286261224253</v>
       </c>
       <c r="E5">
-        <v>-15.47457237690838</v>
+        <v>-15.45384648712285</v>
       </c>
       <c r="F5">
-        <v>4.606494085374763E-06</v>
+        <v>4.642886368475456E-06</v>
       </c>
       <c r="G5">
-        <v>0.9714823929119137</v>
+        <v>0.9714077248880298</v>
       </c>
     </row>
   </sheetData>
